--- a/strategy_packs/garp_senales.xlsx
+++ b/strategy_packs/garp_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Retorno sobre capital invertido (TTM, fracción): &gt;20% → 100; &gt;10% → 60; &gt;5% → 20; positivo → −20; negativo/sin dato → −80.</t>
+          <t>Retorno sobre capital invertido (TTM, fraccion): &gt;20% -&gt; 100; &gt;10% -&gt; 60; &gt;5% -&gt; 20; positivo -&gt; -20; negativo/sin dato -&gt; -80.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Premia P/E TTM bajo pero positivo: &lt;8 → 100; 8-15 → 80; 15-25 → 30; 25-40 → −30; &gt;40 → −80; negativo (pérdidas) → −100.</t>
+          <t>Premia P/E TTM bajo pero positivo: &lt;8 -&gt; 100; 8-15 -&gt; 80; 15-25 -&gt; 30; 25-40 -&gt; -30; &gt;40 -&gt; -80; negativo (perdidas) -&gt; -100.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crecimiento de revenue interanual (fracción) mapeado lineal: −10% → −100; +10% → 0; +30% o más → +100.</t>
+          <t>Crecimiento de revenue interanual (fraccion) mapeado lineal: -10% -&gt; -100; +10% -&gt; 0; +30% o mas -&gt; +100.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -569,6 +569,44 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>{"min": -0.1, "max": 0.3, "clamp": true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tendencia_m</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tendencia mensual</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mapa del regimen de tendencia mensual a score.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>trend_monthly</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
     </row>

--- a/strategy_packs/garp_senales.xlsx
+++ b/strategy_packs/garp_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>params</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>publica</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,7 +484,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>fundamental_roic</t>
@@ -493,6 +497,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>{"thresholds": [[0.2, 100], [0.1, 60], [0.05, 20], [0.0, -20], [null, -80]]}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -517,7 +526,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>fundamental_pe_ttm</t>
@@ -531,6 +539,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>{"thresholds": [[40, -80], [25, -30], [15, 30], [8, 80], [0, 100], [null, -100]]}</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -555,7 +568,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>fundamental_revenue_growth_yoy</t>
@@ -569,6 +581,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>{"min": -0.1, "max": 0.3, "clamp": true}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -593,7 +610,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>trend_monthly</t>
@@ -607,6 +623,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>

--- a/strategy_packs/garp_senales.xlsx
+++ b/strategy_packs/garp_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,30 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>indicator_key</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>group_type</t>
+          <t>formula_type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>indicator_key</t>
+          <t>params</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>formula_type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>params</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>publica</t>
         </is>
@@ -481,25 +471,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>fundamental_roic</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>threshold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fundamental_roic</t>
+          <t>{"thresholds": [[0.2, 100], [0.1, 60], [0.05, 20], [0.0, -20], [null, -80]]}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>{"thresholds": [[0.2, 100], [0.1, 60], [0.05, 20], [0.0, -20], [null, -80]]}</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -523,25 +508,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>fundamental_pe_ttm</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>threshold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fundamental_pe_ttm</t>
+          <t>{"thresholds": [[40, -80], [25, -30], [15, 30], [8, 80], [0, 100], [null, -100]]}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>{"thresholds": [[40, -80], [25, -30], [15, 30], [8, 80], [0, 100], [null, -100]]}</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -565,25 +545,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>fundamental_revenue_growth_yoy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>range</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>fundamental_revenue_growth_yoy</t>
+          <t>{"min": -0.1, "max": 0.3, "clamp": true}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>{"min": -0.1, "max": 0.3, "clamp": true}</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -607,25 +582,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>trend_monthly</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>trend_monthly</t>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>discrete_map</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
